--- a/Data_clean/MCAS/Estados_US/Edos_USA_2016/HAWAII_2016.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2016/HAWAII_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -488,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -501,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -532,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -547,7 +577,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -563,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -576,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -589,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -646,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -661,7 +721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -677,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Otumba</t>
@@ -690,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -703,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C24">
@@ -716,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -729,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -760,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C28">
@@ -773,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -786,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>León</t>
@@ -799,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -812,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
@@ -832,7 +942,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Buenavista de Cuéllar</t>
+          <t>Buenavista De Cuéllar</t>
         </is>
       </c>
       <c r="C33">
@@ -843,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -856,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -887,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -900,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Chapantongo</t>
@@ -913,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -926,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -939,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mineral del Chico</t>
+          <t>Mineral Del Chico</t>
         </is>
       </c>
       <c r="C41">
@@ -952,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Total</t>
@@ -983,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Atotonilco el Alto</t>
+          <t>Atotonilco El Alto</t>
         </is>
       </c>
       <c r="C44">
@@ -996,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -1009,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>El Salto</t>
@@ -1035,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C48">
@@ -1048,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1061,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Hostotipaquillo</t>
@@ -1074,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Jocotepec</t>
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -1100,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -1113,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1126,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C55">
@@ -1139,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -1152,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1165,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C58">
@@ -1178,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -1191,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C60">
@@ -1204,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1235,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1248,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1257,10 +1507,15 @@
         <v>16</v>
       </c>
       <c r="D64">
-        <v>0.09142857142857143</v>
+        <v>0.09142857142857144</v>
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -1274,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -1287,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Tocumbo</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Villamar</t>
@@ -1339,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1352,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1383,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1414,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C76">
@@ -1427,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>La Yesca</t>
@@ -1440,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -1453,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1466,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1486,7 +1806,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C81">
@@ -1497,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -1510,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C83">
@@ -1523,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C84">
@@ -1536,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -1549,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Santo Tomás Ocotepec</t>
@@ -1562,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -1575,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1606,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C90">
@@ -1619,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1632,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -1645,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -1658,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -1671,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Tochtepec</t>
@@ -1684,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1715,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1746,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1777,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>El Fuerte</t>
@@ -1790,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1821,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1852,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1883,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -1896,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Huayacocotla</t>
@@ -1909,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C111">
@@ -1922,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1953,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1976,76 +2421,6 @@
       </c>
       <c r="D115">
         <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
